--- a/research/traditional_assets/database/data/morocco/morocco_insurance_general.xlsx
+++ b/research/traditional_assets/database/data/morocco/morocco_insurance_general.xlsx
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0587</v>
+        <v>0.0548</v>
       </c>
       <c r="E2">
-        <v>0.0559</v>
+        <v>0.005160000000000001</v>
       </c>
       <c r="G2">
-        <v>0.1186187756415413</v>
+        <v>0.1232985265590821</v>
       </c>
       <c r="H2">
-        <v>0.1186187756415413</v>
+        <v>0.1232985265590821</v>
       </c>
       <c r="I2">
-        <v>0.1296798326763736</v>
+        <v>0.06879772173841264</v>
       </c>
       <c r="J2">
-        <v>0.09889149375002054</v>
+        <v>0.04958650755670486</v>
       </c>
       <c r="K2">
-        <v>247.77</v>
+        <v>126.13</v>
       </c>
       <c r="L2">
-        <v>0.09965811278255973</v>
+        <v>0.05205745181394197</v>
       </c>
       <c r="M2">
-        <v>89.4115</v>
+        <v>94.13860000000001</v>
       </c>
       <c r="N2">
-        <v>0.02536496453900709</v>
+        <v>0.03604771204288723</v>
       </c>
       <c r="O2">
-        <v>0.3608649150421763</v>
+        <v>0.7463616903195116</v>
       </c>
       <c r="P2">
-        <v>89.4115</v>
+        <v>94.13860000000001</v>
       </c>
       <c r="Q2">
-        <v>0.02536496453900709</v>
+        <v>0.03604771204288723</v>
       </c>
       <c r="R2">
-        <v>0.3608649150421763</v>
+        <v>0.7463616903195116</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,73 +636,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>82.56999999999999</v>
+        <v>153.17</v>
       </c>
       <c r="V2">
-        <v>0.0234241134751773</v>
+        <v>0.05865211564235114</v>
       </c>
       <c r="W2">
-        <v>0.2874186550976139</v>
+        <v>0.5278846153846154</v>
       </c>
       <c r="X2">
-        <v>0.06353116715844763</v>
+        <v>0.1036669889211395</v>
       </c>
       <c r="Y2">
-        <v>0.2238874879391662</v>
+        <v>0.4242176264634759</v>
       </c>
       <c r="Z2">
-        <v>2.340781302371474</v>
+        <v>2.250880926921851</v>
       </c>
       <c r="AA2">
-        <v>0.2845535234444329</v>
+        <v>1.047930283224401</v>
       </c>
       <c r="AB2">
-        <v>0.06163362984121305</v>
+        <v>0.1013089049953818</v>
       </c>
       <c r="AC2">
-        <v>0.2229198936032199</v>
+        <v>0.9469112018045734</v>
       </c>
       <c r="AD2">
-        <v>109.763</v>
+        <v>155.44</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>109.763</v>
+        <v>155.44</v>
       </c>
       <c r="AG2">
-        <v>27.19300000000001</v>
+        <v>2.269999999999982</v>
       </c>
       <c r="AH2">
-        <v>0.03019811745635135</v>
+        <v>0.0561775824557092</v>
       </c>
       <c r="AI2">
-        <v>0.07007015122507698</v>
+        <v>0.1009573542210618</v>
       </c>
       <c r="AJ2">
-        <v>0.007655270983305246</v>
+        <v>0.0008684773335067668</v>
       </c>
       <c r="AK2">
-        <v>0.01832532180337934</v>
+        <v>0.001637227819890502</v>
       </c>
       <c r="AL2">
-        <v>0.648</v>
+        <v>0.548</v>
       </c>
       <c r="AM2">
-        <v>0.648</v>
+        <v>0.03600000000000003</v>
       </c>
       <c r="AN2">
-        <v>0.2545701231532806</v>
+        <v>0.7124392703272527</v>
       </c>
       <c r="AO2">
-        <v>497.5462962962963</v>
+        <v>304.1788321167883</v>
       </c>
       <c r="AP2">
-        <v>0.06306793144235455</v>
+        <v>0.01040425336877799</v>
       </c>
       <c r="AQ2">
-        <v>497.5462962962963</v>
+        <v>4630.277777777774</v>
       </c>
     </row>
     <row r="3">
@@ -713,7 +713,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Agma SA (CBSE:AGM)</t>
+          <t>AtlantaSanad Société Anonyme (CBSE:ATL)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -722,46 +722,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.045</v>
+        <v>0.09810000000000001</v>
       </c>
       <c r="E3">
-        <v>0.0559</v>
+        <v>0.221</v>
       </c>
       <c r="G3">
-        <v>0.5517006802721088</v>
+        <v>0.1311475409836066</v>
       </c>
       <c r="H3">
-        <v>0.5517006802721088</v>
+        <v>0.1311475409836066</v>
       </c>
       <c r="I3">
-        <v>0.5374149659863946</v>
+        <v>0.1045901639344262</v>
       </c>
       <c r="J3">
-        <v>0.3676362404013853</v>
+        <v>0.07405049283269424</v>
       </c>
       <c r="K3">
-        <v>5.63</v>
+        <v>45</v>
       </c>
       <c r="L3">
-        <v>0.3829931972789116</v>
+        <v>0.07377049180327869</v>
       </c>
       <c r="M3">
-        <v>5.28</v>
+        <v>33.8886</v>
       </c>
       <c r="N3">
-        <v>0.05161290322580646</v>
+        <v>0.04698918469217971</v>
       </c>
       <c r="O3">
-        <v>0.9378330373001776</v>
+        <v>0.7530800000000001</v>
       </c>
       <c r="P3">
-        <v>5.28</v>
+        <v>33.8886</v>
       </c>
       <c r="Q3">
-        <v>0.05161290322580646</v>
+        <v>0.04698918469217971</v>
       </c>
       <c r="R3">
-        <v>0.9378330373001776</v>
+        <v>0.7530800000000001</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -776,10 +776,10 @@
         <v>0</v>
       </c>
       <c r="X3">
-        <v>0.06155959961884331</v>
+        <v>0.101436712212095</v>
       </c>
       <c r="AB3">
-        <v>0.06155959961884331</v>
+        <v>0.101436712212095</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -800,22 +800,16 @@
         <v>0</v>
       </c>
       <c r="AL3">
-        <v>0.012</v>
+        <v>0</v>
       </c>
       <c r="AM3">
-        <v>0.012</v>
+        <v>0</v>
       </c>
       <c r="AN3">
         <v>0</v>
       </c>
-      <c r="AO3">
-        <v>658.3333333333334</v>
-      </c>
       <c r="AP3">
         <v>0</v>
-      </c>
-      <c r="AQ3">
-        <v>658.3333333333334</v>
       </c>
     </row>
     <row r="4">
@@ -826,7 +820,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>AFMA S.A. (CBSE:AFM)</t>
+          <t>Agma SA (CBSE:AGM)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -835,121 +829,106 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0256</v>
+        <v>0.0572</v>
       </c>
       <c r="E4">
-        <v>-0.0491</v>
+        <v>0.05860000000000001</v>
       </c>
       <c r="G4">
-        <v>0.4415584415584415</v>
+        <v>0.5798657718120805</v>
       </c>
       <c r="H4">
-        <v>0.4415584415584415</v>
+        <v>0.5798657718120805</v>
       </c>
       <c r="I4">
-        <v>0.4116883116883117</v>
+        <v>0.5375838926174497</v>
       </c>
       <c r="J4">
-        <v>0.2728875450249496</v>
+        <v>0.3689169463087248</v>
       </c>
       <c r="K4">
-        <v>5.04</v>
+        <v>5.49</v>
       </c>
       <c r="L4">
-        <v>0.2181818181818182</v>
+        <v>0.3684563758389262</v>
       </c>
       <c r="M4">
-        <v>5.26</v>
+        <v>-0</v>
       </c>
       <c r="N4">
-        <v>0.03578231292517007</v>
+        <v>-0</v>
       </c>
       <c r="O4">
-        <v>1.043650793650793</v>
+        <v>-0</v>
       </c>
       <c r="P4">
-        <v>5.26</v>
+        <v>-0</v>
       </c>
       <c r="Q4">
-        <v>0.03578231292517007</v>
+        <v>-0</v>
       </c>
       <c r="R4">
-        <v>1.043650793650793</v>
+        <v>-0</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
       <c r="U4">
-        <v>4.01</v>
+        <v>3.43</v>
       </c>
       <c r="V4">
-        <v>0.02727891156462585</v>
+        <v>0.02951807228915663</v>
       </c>
       <c r="W4">
-        <v>2.597938144329897</v>
+        <v>0.5278846153846154</v>
       </c>
       <c r="X4">
-        <v>0.06491796496271969</v>
+        <v>0.1027161829531159</v>
       </c>
       <c r="Y4">
-        <v>2.533020179367177</v>
-      </c>
-      <c r="Z4">
-        <v>2.789855072463768</v>
-      </c>
-      <c r="AA4">
-        <v>0.7613167017000404</v>
+        <v>0.4251684324314995</v>
       </c>
       <c r="AB4">
-        <v>0.06168076466088558</v>
-      </c>
-      <c r="AC4">
-        <v>0.6996359370391548</v>
+        <v>0.1013089049953818</v>
       </c>
       <c r="AD4">
-        <v>15.4</v>
+        <v>3.44</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>15.4</v>
+        <v>3.44</v>
       </c>
       <c r="AG4">
-        <v>11.39</v>
+        <v>0.009999999999999787</v>
       </c>
       <c r="AH4">
-        <v>0.09482758620689655</v>
+        <v>0.02875292544299565</v>
       </c>
       <c r="AI4">
-        <v>0.8845491097070649</v>
+        <v>0.2749800159872102</v>
       </c>
       <c r="AJ4">
-        <v>0.07191110549908455</v>
+        <v>8.605111436192914e-05</v>
       </c>
       <c r="AK4">
-        <v>0.85</v>
+        <v>0.00110132158590306</v>
       </c>
       <c r="AL4">
-        <v>0.628</v>
+        <v>0</v>
       </c>
       <c r="AM4">
-        <v>0.628</v>
+        <v>-0.512</v>
       </c>
       <c r="AN4">
-        <v>1.546184738955823</v>
-      </c>
-      <c r="AO4">
-        <v>15.14331210191083</v>
+        <v>0.4105011933174224</v>
       </c>
       <c r="AP4">
-        <v>1.143574297188755</v>
+        <v>0.001193317422434342</v>
       </c>
       <c r="AQ4">
-        <v>15.14331210191083</v>
+        <v>-15.64453125</v>
       </c>
     </row>
     <row r="5">
@@ -960,7 +939,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>AtlantaSanad Société Anonyme (CBSE:ATL)</t>
+          <t>AFMA S.A. (CBSE:AFM)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -969,46 +948,46 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.09880000000000001</v>
+        <v>0.0539</v>
       </c>
       <c r="E5">
-        <v>0.277</v>
+        <v>0.005160000000000001</v>
       </c>
       <c r="G5">
-        <v>0.1338845883180859</v>
+        <v>0.4472573839662447</v>
       </c>
       <c r="H5">
-        <v>0.1338845883180859</v>
+        <v>0.4472573839662447</v>
       </c>
       <c r="I5">
-        <v>0.1032723434201267</v>
+        <v>0.4168776371308017</v>
       </c>
       <c r="J5">
-        <v>0.09795169316878563</v>
+        <v>0.2856383809970308</v>
       </c>
       <c r="K5">
-        <v>53</v>
+        <v>6.03</v>
       </c>
       <c r="L5">
-        <v>0.09324419422941591</v>
+        <v>0.2544303797468355</v>
       </c>
       <c r="M5">
-        <v>30.4515</v>
+        <v>5.35</v>
       </c>
       <c r="N5">
-        <v>0.03829895610615017</v>
+        <v>0.0430064308681672</v>
       </c>
       <c r="O5">
-        <v>0.5745566037735849</v>
+        <v>0.8872305140961857</v>
       </c>
       <c r="P5">
-        <v>30.4515</v>
+        <v>5.35</v>
       </c>
       <c r="Q5">
-        <v>0.03829895610615017</v>
+        <v>0.0430064308681672</v>
       </c>
       <c r="R5">
-        <v>0.5745566037735849</v>
+        <v>0.8872305140961857</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -1017,67 +996,73 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>5.56</v>
+        <v>2.04</v>
       </c>
       <c r="V5">
-        <v>0.006992831090428876</v>
+        <v>0.01639871382636656</v>
       </c>
       <c r="W5">
-        <v>0.2874186550976139</v>
+        <v>3.241935483870968</v>
       </c>
       <c r="X5">
-        <v>0.06353116715844763</v>
+        <v>0.105918459602769</v>
       </c>
       <c r="Y5">
-        <v>0.2238874879391662</v>
+        <v>3.136017024268198</v>
       </c>
       <c r="Z5">
-        <v>2.905039353981396</v>
+        <v>3.668730650154798</v>
       </c>
       <c r="AA5">
-        <v>0.2845535234444329</v>
+        <v>1.047930283224401</v>
       </c>
       <c r="AB5">
-        <v>0.06163362984121305</v>
+        <v>0.1010190814198272</v>
       </c>
       <c r="AC5">
-        <v>0.2229198936032199</v>
+        <v>0.9469112018045734</v>
       </c>
       <c r="AD5">
-        <v>48.9</v>
+        <v>12.9</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>48.9</v>
+        <v>12.9</v>
       </c>
       <c r="AG5">
-        <v>43.34</v>
+        <v>10.86</v>
       </c>
       <c r="AH5">
-        <v>0.05793838862559242</v>
+        <v>0.09395484340859431</v>
       </c>
       <c r="AI5">
-        <v>0.1817843866171004</v>
+        <v>0.8295819935691319</v>
       </c>
       <c r="AJ5">
-        <v>0.05169123610514765</v>
+        <v>0.08028981221351471</v>
       </c>
       <c r="AK5">
-        <v>0.1645156392347404</v>
+        <v>0.8038490007401924</v>
       </c>
       <c r="AL5">
-        <v>0</v>
+        <v>0.548</v>
       </c>
       <c r="AM5">
-        <v>0</v>
+        <v>0.548</v>
       </c>
       <c r="AN5">
-        <v>0.6425755584756899</v>
+        <v>1.252427184466019</v>
+      </c>
+      <c r="AO5">
+        <v>18.02919708029197</v>
       </c>
       <c r="AP5">
-        <v>0.5695137976346912</v>
+        <v>1.054368932038835</v>
+      </c>
+      <c r="AQ5">
+        <v>18.02919708029197</v>
       </c>
     </row>
     <row r="6">
@@ -1088,7 +1073,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SAHAM Assurance S.A. (CBSE:SAH)</t>
+          <t>Wafa Assurance SA (CBSE:WAA)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1097,46 +1082,46 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.0842</v>
+        <v>0.0548</v>
       </c>
       <c r="E6">
-        <v>0.132</v>
+        <v>-0.07539999999999999</v>
       </c>
       <c r="G6">
-        <v>0.06147267138848056</v>
+        <v>0.05265835665225134</v>
       </c>
       <c r="H6">
-        <v>0.06147267138848056</v>
+        <v>0.05265835665225134</v>
       </c>
       <c r="I6">
-        <v>0.1449953227315248</v>
+        <v>0.05961163402018146</v>
       </c>
       <c r="J6">
-        <v>0.1022556545985409</v>
+        <v>0.05375222589671839</v>
       </c>
       <c r="K6">
-        <v>76.8</v>
+        <v>59.7</v>
       </c>
       <c r="L6">
-        <v>0.1026326339703328</v>
+        <v>0.05062325108114984</v>
       </c>
       <c r="M6">
-        <v>9.220000000000001</v>
+        <v>41.6</v>
       </c>
       <c r="N6">
-        <v>0.01428571428571429</v>
+        <v>0.03302635757383297</v>
       </c>
       <c r="O6">
-        <v>0.1200520833333334</v>
+        <v>0.6968174204355109</v>
       </c>
       <c r="P6">
-        <v>9.220000000000001</v>
+        <v>41.6</v>
       </c>
       <c r="Q6">
-        <v>0.01428571428571429</v>
+        <v>0.03302635757383297</v>
       </c>
       <c r="R6">
-        <v>0.1200520833333334</v>
+        <v>0.6968174204355109</v>
       </c>
       <c r="S6">
         <v>0</v>
@@ -1145,55 +1130,55 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>39.5</v>
+        <v>87.7</v>
       </c>
       <c r="V6">
-        <v>0.06120235512860242</v>
+        <v>0.06962527786598921</v>
       </c>
       <c r="W6">
-        <v>0.1673567225975158</v>
+        <v>0.08895842646401431</v>
       </c>
       <c r="X6">
-        <v>0.06379475699127139</v>
+        <v>0.1036669889211395</v>
       </c>
       <c r="Y6">
-        <v>0.1035619656062444</v>
+        <v>-0.01470856245712517</v>
       </c>
       <c r="Z6">
-        <v>2.227746353081274</v>
+        <v>1.848250094426412</v>
       </c>
       <c r="AA6">
-        <v>0.2277996616138379</v>
+        <v>0.09934755658923962</v>
       </c>
       <c r="AB6">
-        <v>0.06164288223754402</v>
+        <v>0.101218588969648</v>
       </c>
       <c r="AC6">
-        <v>0.1661567793762939</v>
+        <v>-0.001871032380408366</v>
       </c>
       <c r="AD6">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="AG6">
-        <v>5.5</v>
+        <v>-22.7</v>
       </c>
       <c r="AH6">
-        <v>0.06517960602549247</v>
+        <v>0.04907141778650159</v>
       </c>
       <c r="AI6">
-        <v>0.07395234182415776</v>
+        <v>0.06934072967783231</v>
       </c>
       <c r="AJ6">
-        <v>0.008449838684897834</v>
+        <v>-0.01835233244401326</v>
       </c>
       <c r="AK6">
-        <v>0.009666080843585237</v>
+        <v>-0.02671531128633636</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1202,10 +1187,10 @@
         <v>0</v>
       </c>
       <c r="AN6">
-        <v>0.3294289897510981</v>
+        <v>0.8217446270543616</v>
       </c>
       <c r="AP6">
-        <v>0.04026354319180088</v>
+        <v>-0.2869785082174463</v>
       </c>
     </row>
     <row r="7">
@@ -1216,7 +1201,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Wafa Assurance SA (CBSE:WAA)</t>
+          <t>Sanlam Maroc (CBSE:SAH)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1225,46 +1210,46 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.0587</v>
+        <v>0.0166</v>
       </c>
       <c r="E7">
-        <v>0.0283</v>
+        <v>-0.222</v>
       </c>
       <c r="G7">
-        <v>0.1365202792259433</v>
+        <v>0.2309243697478992</v>
       </c>
       <c r="H7">
-        <v>0.1365202792259433</v>
+        <v>0.2309243697478992</v>
       </c>
       <c r="I7">
-        <v>0.1217637182999028</v>
+        <v>0.02470588235294117</v>
       </c>
       <c r="J7">
-        <v>0.09890421630264626</v>
+        <v>0.01538290788013319</v>
       </c>
       <c r="K7">
-        <v>107.3</v>
+        <v>9.91</v>
       </c>
       <c r="L7">
-        <v>0.09481311301581691</v>
+        <v>0.01665546218487395</v>
       </c>
       <c r="M7">
-        <v>39.2</v>
+        <v>13.3</v>
       </c>
       <c r="N7">
-        <v>0.02136006974716652</v>
+        <v>0.03409382209689823</v>
       </c>
       <c r="O7">
-        <v>0.3653308480894688</v>
+        <v>1.342078708375378</v>
       </c>
       <c r="P7">
-        <v>39.2</v>
+        <v>13.3</v>
       </c>
       <c r="Q7">
-        <v>0.02136006974716652</v>
+        <v>0.03409382209689823</v>
       </c>
       <c r="R7">
-        <v>0.3653308480894688</v>
+        <v>1.342078708375378</v>
       </c>
       <c r="S7">
         <v>0</v>
@@ -1273,73 +1258,67 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>33.5</v>
+        <v>60</v>
       </c>
       <c r="V7">
-        <v>0.01825414123801221</v>
+        <v>0.1538067162266085</v>
       </c>
       <c r="W7">
-        <v>0.1932636887608069</v>
+        <v>0.01758651286601597</v>
       </c>
       <c r="X7">
-        <v>0.06156768726503459</v>
+        <v>0.1096462801656766</v>
       </c>
       <c r="Y7">
-        <v>0.1316960014957723</v>
+        <v>-0.09205976729966064</v>
       </c>
       <c r="Z7">
-        <v>2.166828775149152</v>
+        <v>1.377633711507293</v>
       </c>
       <c r="AA7">
-        <v>0.2143085018681498</v>
+        <v>0.02119201247668267</v>
       </c>
       <c r="AB7">
-        <v>0.0615599218968569</v>
+        <v>0.1019938164914625</v>
       </c>
       <c r="AC7">
-        <v>0.1527485799712929</v>
+        <v>-0.08080180401477978</v>
       </c>
       <c r="AD7">
-        <v>0.463</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>0.463</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="AG7">
-        <v>-33.037</v>
+        <v>14.09999999999999</v>
       </c>
       <c r="AH7">
-        <v>0.0002522249454284365</v>
+        <v>0.1596294700560103</v>
       </c>
       <c r="AI7">
-        <v>0.0006894364341096814</v>
+        <v>0.1290491118077325</v>
       </c>
       <c r="AJ7">
-        <v>-0.01833186010366432</v>
+        <v>0.03488372093023254</v>
       </c>
       <c r="AK7">
-        <v>-0.05177701888371524</v>
+        <v>0.02742123687281212</v>
       </c>
       <c r="AL7">
-        <v>0.008</v>
+        <v>0</v>
       </c>
       <c r="AM7">
-        <v>0.008</v>
+        <v>0</v>
       </c>
       <c r="AN7">
-        <v>0.002310379241516966</v>
-      </c>
-      <c r="AO7">
-        <v>17225</v>
+        <v>1.834158415841584</v>
       </c>
       <c r="AP7">
-        <v>-0.1648552894211577</v>
-      </c>
-      <c r="AQ7">
-        <v>17225</v>
+        <v>0.3490099009900989</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/morocco/morocco_insurance_general.xlsx
+++ b/research/traditional_assets/database/data/morocco/morocco_insurance_general.xlsx
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0548</v>
+        <v>0.0572</v>
       </c>
       <c r="E2">
-        <v>0.005160000000000001</v>
+        <v>0.0326</v>
       </c>
       <c r="G2">
-        <v>0.1232985265590821</v>
+        <v>0.08662845445240533</v>
       </c>
       <c r="H2">
-        <v>0.1232985265590821</v>
+        <v>0.08662845445240533</v>
       </c>
       <c r="I2">
-        <v>0.06879772173841264</v>
+        <v>0.09084544524053223</v>
       </c>
       <c r="J2">
-        <v>0.04958650755670486</v>
+        <v>0.06919584352474457</v>
       </c>
       <c r="K2">
-        <v>126.13</v>
+        <v>156.51</v>
       </c>
       <c r="L2">
-        <v>0.05205745181394197</v>
+        <v>0.06407778915046058</v>
       </c>
       <c r="M2">
-        <v>94.13860000000001</v>
+        <v>61.75</v>
       </c>
       <c r="N2">
-        <v>0.03604771204288723</v>
+        <v>0.02068330262937531</v>
       </c>
       <c r="O2">
-        <v>0.7463616903195116</v>
+        <v>0.3945434796498626</v>
       </c>
       <c r="P2">
-        <v>94.13860000000001</v>
+        <v>61.75</v>
       </c>
       <c r="Q2">
-        <v>0.03604771204288723</v>
+        <v>0.02068330262937531</v>
       </c>
       <c r="R2">
-        <v>0.7463616903195116</v>
+        <v>0.3945434796498626</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,73 +636,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>153.17</v>
+        <v>169.589</v>
       </c>
       <c r="V2">
-        <v>0.05865211564235114</v>
+        <v>0.0568042203985932</v>
       </c>
       <c r="W2">
-        <v>0.5278846153846154</v>
+        <v>0.1975421028675467</v>
       </c>
       <c r="X2">
-        <v>0.1036669889211395</v>
+        <v>0.09265845657407197</v>
       </c>
       <c r="Y2">
-        <v>0.4242176264634759</v>
+        <v>0.1048836462934747</v>
       </c>
       <c r="Z2">
-        <v>2.250880926921851</v>
+        <v>1.47485411473731</v>
       </c>
       <c r="AA2">
-        <v>1.047930283224401</v>
+        <v>0.1930746555251313</v>
       </c>
       <c r="AB2">
-        <v>0.1013089049953818</v>
+        <v>0.09019161978602795</v>
       </c>
       <c r="AC2">
-        <v>0.9469112018045734</v>
+        <v>0.1028830357391033</v>
       </c>
       <c r="AD2">
-        <v>155.44</v>
+        <v>167.17</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>155.44</v>
+        <v>167.17</v>
       </c>
       <c r="AG2">
-        <v>2.269999999999982</v>
+        <v>-2.418999999999983</v>
       </c>
       <c r="AH2">
-        <v>0.0561775824557092</v>
+        <v>0.05302489635769047</v>
       </c>
       <c r="AI2">
-        <v>0.1009573542210618</v>
+        <v>0.09804979618170621</v>
       </c>
       <c r="AJ2">
-        <v>0.0008684773335067668</v>
+        <v>-0.0008109065761204549</v>
       </c>
       <c r="AK2">
-        <v>0.001637227819890502</v>
+        <v>-0.001575525234781907</v>
       </c>
       <c r="AL2">
-        <v>0.548</v>
+        <v>0.734</v>
       </c>
       <c r="AM2">
-        <v>0.03600000000000003</v>
+        <v>0.331</v>
       </c>
       <c r="AN2">
-        <v>0.7124392703272527</v>
+        <v>0.6143922966665442</v>
       </c>
       <c r="AO2">
-        <v>304.1788321167883</v>
+        <v>302.3024523160763</v>
       </c>
       <c r="AP2">
-        <v>0.01040425336877799</v>
+        <v>-0.00889044066301585</v>
       </c>
       <c r="AQ2">
-        <v>4630.277777777774</v>
+        <v>670.3625377643505</v>
       </c>
     </row>
     <row r="3">
@@ -713,7 +713,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>AtlantaSanad Société Anonyme (CBSE:ATL)</t>
+          <t>Agma SA (CBSE:AGM)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -722,94 +722,109 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.09810000000000001</v>
+        <v>0.0572</v>
       </c>
       <c r="E3">
-        <v>0.221</v>
+        <v>0.0529</v>
       </c>
       <c r="G3">
-        <v>0.1311475409836066</v>
+        <v>0.5262820512820513</v>
       </c>
       <c r="H3">
-        <v>0.1311475409836066</v>
+        <v>0.5262820512820513</v>
       </c>
       <c r="I3">
-        <v>0.1045901639344262</v>
+        <v>0.5570512820512821</v>
       </c>
       <c r="J3">
-        <v>0.07405049283269424</v>
+        <v>0.4005029123881583</v>
       </c>
       <c r="K3">
-        <v>45</v>
+        <v>6.14</v>
       </c>
       <c r="L3">
-        <v>0.07377049180327869</v>
+        <v>0.3935897435897436</v>
       </c>
       <c r="M3">
-        <v>33.8886</v>
+        <v>-0</v>
       </c>
       <c r="N3">
-        <v>0.04698918469217971</v>
+        <v>-0</v>
       </c>
       <c r="O3">
-        <v>0.7530800000000001</v>
+        <v>-0</v>
       </c>
       <c r="P3">
-        <v>33.8886</v>
+        <v>-0</v>
       </c>
       <c r="Q3">
-        <v>0.04698918469217971</v>
+        <v>-0</v>
       </c>
       <c r="R3">
-        <v>0.7530800000000001</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
       <c r="U3">
-        <v>0</v>
+        <v>0.349</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>0.002699149265274555</v>
+      </c>
+      <c r="W3">
+        <v>0.6769570011025358</v>
       </c>
       <c r="X3">
-        <v>0.101436712212095</v>
+        <v>0.09162270864054253</v>
+      </c>
+      <c r="Y3">
+        <v>0.5853342924619932</v>
       </c>
       <c r="AB3">
-        <v>0.101436712212095</v>
+        <v>0.08999072037382369</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>5.17</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>5.17</v>
       </c>
       <c r="AG3">
-        <v>0</v>
+        <v>4.821</v>
       </c>
       <c r="AH3">
-        <v>0</v>
+        <v>0.03844723730200045</v>
+      </c>
+      <c r="AI3">
+        <v>0.3385723641126392</v>
       </c>
       <c r="AJ3">
-        <v>0</v>
+        <v>0.03594515400272887</v>
+      </c>
+      <c r="AK3">
+        <v>0.3231016687889551</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="AM3">
-        <v>0</v>
+        <v>-0.398</v>
       </c>
       <c r="AN3">
-        <v>0</v>
+        <v>0.5815523059617548</v>
+      </c>
+      <c r="AO3">
+        <v>1738</v>
       </c>
       <c r="AP3">
-        <v>0</v>
+        <v>0.5422947131608549</v>
+      </c>
+      <c r="AQ3">
+        <v>-21.83417085427136</v>
       </c>
     </row>
     <row r="4">
@@ -820,7 +835,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Agma SA (CBSE:AGM)</t>
+          <t>AFMA S.A. (CBSE:AFM)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -829,106 +844,121 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0572</v>
+        <v>0.0607</v>
       </c>
       <c r="E4">
-        <v>0.05860000000000001</v>
+        <v>0.0326</v>
       </c>
       <c r="G4">
-        <v>0.5798657718120805</v>
+        <v>0.396078431372549</v>
       </c>
       <c r="H4">
-        <v>0.5798657718120805</v>
+        <v>0.396078431372549</v>
       </c>
       <c r="I4">
-        <v>0.5375838926174497</v>
+        <v>0.4196078431372549</v>
       </c>
       <c r="J4">
-        <v>0.3689169463087248</v>
+        <v>0.2850737820901556</v>
       </c>
       <c r="K4">
-        <v>5.49</v>
+        <v>6.37</v>
       </c>
       <c r="L4">
-        <v>0.3684563758389262</v>
+        <v>0.2498039215686275</v>
       </c>
       <c r="M4">
-        <v>-0</v>
+        <v>5.55</v>
       </c>
       <c r="N4">
-        <v>-0</v>
+        <v>0.04564144736842105</v>
       </c>
       <c r="O4">
-        <v>-0</v>
+        <v>0.8712715855572998</v>
       </c>
       <c r="P4">
-        <v>-0</v>
+        <v>5.55</v>
       </c>
       <c r="Q4">
-        <v>-0</v>
+        <v>0.04564144736842105</v>
       </c>
       <c r="R4">
-        <v>-0</v>
+        <v>0.8712715855572998</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
       <c r="U4">
-        <v>3.43</v>
+        <v>2.04</v>
       </c>
       <c r="V4">
-        <v>0.02951807228915663</v>
+        <v>0.01677631578947368</v>
       </c>
       <c r="W4">
-        <v>0.5278846153846154</v>
+        <v>2.687763713080169</v>
       </c>
       <c r="X4">
-        <v>0.1027161829531159</v>
+        <v>0.09468185717896302</v>
       </c>
       <c r="Y4">
-        <v>0.4251684324314995</v>
+        <v>2.593081855901206</v>
+      </c>
+      <c r="Z4">
+        <v>3.935185185185185</v>
+      </c>
+      <c r="AA4">
+        <v>1.12181812396589</v>
       </c>
       <c r="AB4">
-        <v>0.1013089049953818</v>
+        <v>0.09018905649157644</v>
+      </c>
+      <c r="AC4">
+        <v>1.031629067474314</v>
       </c>
       <c r="AD4">
-        <v>3.44</v>
+        <v>15.5</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>3.44</v>
+        <v>15.5</v>
       </c>
       <c r="AG4">
-        <v>0.009999999999999787</v>
+        <v>13.46</v>
       </c>
       <c r="AH4">
-        <v>0.02875292544299565</v>
+        <v>0.113056163384391</v>
       </c>
       <c r="AI4">
-        <v>0.2749800159872102</v>
+        <v>0.8166491043203372</v>
       </c>
       <c r="AJ4">
-        <v>8.605111436192914e-05</v>
+        <v>0.09965941063231157</v>
       </c>
       <c r="AK4">
-        <v>0.00110132158590306</v>
+        <v>0.79456906729634</v>
       </c>
       <c r="AL4">
-        <v>0</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="AM4">
-        <v>-0.512</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="AN4">
-        <v>0.4105011933174224</v>
+        <v>1.371681415929203</v>
+      </c>
+      <c r="AO4">
+        <v>15.55232558139535</v>
       </c>
       <c r="AP4">
-        <v>0.001193317422434342</v>
+        <v>1.191150442477876</v>
       </c>
       <c r="AQ4">
-        <v>-15.64453125</v>
+        <v>15.55232558139535</v>
       </c>
     </row>
     <row r="5">
@@ -939,7 +969,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>AFMA S.A. (CBSE:AFM)</t>
+          <t>AtlantaSanad Société Anonyme (CBSE:ATL)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -948,121 +978,112 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.0539</v>
+        <v>0.0335</v>
       </c>
       <c r="E5">
-        <v>0.005160000000000001</v>
+        <v>0.145</v>
       </c>
       <c r="G5">
-        <v>0.4472573839662447</v>
+        <v>0.1685393258426966</v>
       </c>
       <c r="H5">
-        <v>0.4472573839662447</v>
+        <v>0.1685393258426966</v>
       </c>
       <c r="I5">
-        <v>0.4168776371308017</v>
+        <v>0.1381247578457962</v>
       </c>
       <c r="J5">
-        <v>0.2856383809970308</v>
+        <v>0.09523570087138496</v>
       </c>
       <c r="K5">
-        <v>6.03</v>
+        <v>43.4</v>
       </c>
       <c r="L5">
-        <v>0.2544303797468355</v>
+        <v>0.08407593955831072</v>
       </c>
       <c r="M5">
-        <v>5.35</v>
+        <v>-0</v>
       </c>
       <c r="N5">
-        <v>0.0430064308681672</v>
+        <v>-0</v>
       </c>
       <c r="O5">
-        <v>0.8872305140961857</v>
+        <v>-0</v>
       </c>
       <c r="P5">
-        <v>5.35</v>
+        <v>-0</v>
       </c>
       <c r="Q5">
-        <v>0.0430064308681672</v>
+        <v>-0</v>
       </c>
       <c r="R5">
-        <v>0.8872305140961857</v>
+        <v>-0</v>
       </c>
       <c r="S5">
         <v>0</v>
       </c>
-      <c r="T5">
-        <v>0</v>
-      </c>
       <c r="U5">
-        <v>2.04</v>
+        <v>31.3</v>
       </c>
       <c r="V5">
-        <v>0.01639871382636656</v>
+        <v>0.04034544985821088</v>
       </c>
       <c r="W5">
-        <v>3.241935483870968</v>
+        <v>0.1975421028675467</v>
       </c>
       <c r="X5">
-        <v>0.105918459602769</v>
+        <v>0.09432175927855628</v>
       </c>
       <c r="Y5">
-        <v>3.136017024268198</v>
+        <v>0.1032203435889904</v>
       </c>
       <c r="Z5">
-        <v>3.668730650154798</v>
+        <v>2.027334851936219</v>
       </c>
       <c r="AA5">
-        <v>1.047930283224401</v>
+        <v>0.1930746555251313</v>
       </c>
       <c r="AB5">
-        <v>0.1010190814198272</v>
+        <v>0.09019161978602795</v>
       </c>
       <c r="AC5">
-        <v>0.9469112018045734</v>
+        <v>0.1028830357391033</v>
       </c>
       <c r="AD5">
-        <v>12.9</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>12.9</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="AG5">
-        <v>10.86</v>
+        <v>59.60000000000001</v>
       </c>
       <c r="AH5">
-        <v>0.09395484340859431</v>
+        <v>0.1048805815160956</v>
       </c>
       <c r="AI5">
-        <v>0.8295819935691319</v>
+        <v>0.3005952380952381</v>
       </c>
       <c r="AJ5">
-        <v>0.08028981221351471</v>
+        <v>0.07134306918841275</v>
       </c>
       <c r="AK5">
-        <v>0.8038490007401924</v>
+        <v>0.2198450756178532</v>
       </c>
       <c r="AL5">
-        <v>0.548</v>
+        <v>0</v>
       </c>
       <c r="AM5">
-        <v>0.548</v>
+        <v>0</v>
       </c>
       <c r="AN5">
-        <v>1.252427184466019</v>
-      </c>
-      <c r="AO5">
-        <v>18.02919708029197</v>
+        <v>0.9053784860557769</v>
       </c>
       <c r="AP5">
-        <v>1.054368932038835</v>
-      </c>
-      <c r="AQ5">
-        <v>18.02919708029197</v>
+        <v>0.5936254980079682</v>
       </c>
     </row>
     <row r="6">
@@ -1082,46 +1103,46 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.0548</v>
+        <v>0.07730000000000001</v>
       </c>
       <c r="E6">
-        <v>-0.07539999999999999</v>
+        <v>-0.0107</v>
       </c>
       <c r="G6">
-        <v>0.05265835665225134</v>
+        <v>0.09011788907350265</v>
       </c>
       <c r="H6">
-        <v>0.05265835665225134</v>
+        <v>0.09011788907350265</v>
       </c>
       <c r="I6">
-        <v>0.05961163402018146</v>
+        <v>0.08268059181897301</v>
       </c>
       <c r="J6">
-        <v>0.05375222589671839</v>
+        <v>0.06250494501147241</v>
       </c>
       <c r="K6">
-        <v>59.7</v>
+        <v>74.3</v>
       </c>
       <c r="L6">
-        <v>0.05062325108114984</v>
+        <v>0.05878629638420761</v>
       </c>
       <c r="M6">
-        <v>41.6</v>
+        <v>40.2</v>
       </c>
       <c r="N6">
-        <v>0.03302635757383297</v>
+        <v>0.02833779782884534</v>
       </c>
       <c r="O6">
-        <v>0.6968174204355109</v>
+        <v>0.541049798115747</v>
       </c>
       <c r="P6">
-        <v>41.6</v>
+        <v>40.2</v>
       </c>
       <c r="Q6">
-        <v>0.03302635757383297</v>
+        <v>0.02833779782884534</v>
       </c>
       <c r="R6">
-        <v>0.6968174204355109</v>
+        <v>0.541049798115747</v>
       </c>
       <c r="S6">
         <v>0</v>
@@ -1130,55 +1151,55 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>87.7</v>
+        <v>91.7</v>
       </c>
       <c r="V6">
-        <v>0.06962527786598921</v>
+        <v>0.06464119554490343</v>
       </c>
       <c r="W6">
-        <v>0.08895842646401431</v>
+        <v>0.07474097173322602</v>
       </c>
       <c r="X6">
-        <v>0.1036669889211395</v>
+        <v>0.09066820523287544</v>
       </c>
       <c r="Y6">
-        <v>-0.01470856245712517</v>
+        <v>-0.01592723349964942</v>
       </c>
       <c r="Z6">
-        <v>1.848250094426412</v>
+        <v>1.261130557296178</v>
       </c>
       <c r="AA6">
-        <v>0.09934755658923962</v>
+        <v>0.07882689613608515</v>
       </c>
       <c r="AB6">
-        <v>0.101218588969648</v>
+        <v>0.09022057464257603</v>
       </c>
       <c r="AC6">
-        <v>-0.001871032380408366</v>
+        <v>-0.01139367850649088</v>
       </c>
       <c r="AD6">
-        <v>65</v>
+        <v>18</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>65</v>
+        <v>18</v>
       </c>
       <c r="AG6">
-        <v>-22.7</v>
+        <v>-73.7</v>
       </c>
       <c r="AH6">
-        <v>0.04907141778650159</v>
+        <v>0.01252958373938466</v>
       </c>
       <c r="AI6">
-        <v>0.06934072967783231</v>
+        <v>0.02211030585923105</v>
       </c>
       <c r="AJ6">
-        <v>-0.01835233244401326</v>
+        <v>-0.05479961335415273</v>
       </c>
       <c r="AK6">
-        <v>-0.02671531128633636</v>
+        <v>-0.1020210409745294</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1187,10 +1208,10 @@
         <v>0</v>
       </c>
       <c r="AN6">
-        <v>0.8217446270543616</v>
+        <v>0.1580333625987708</v>
       </c>
       <c r="AP6">
-        <v>-0.2869785082174463</v>
+        <v>-0.6470588235294118</v>
       </c>
     </row>
     <row r="7">
@@ -1210,46 +1231,46 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.0166</v>
+        <v>0.00774</v>
       </c>
       <c r="E7">
-        <v>-0.222</v>
+        <v>-0.152</v>
       </c>
       <c r="G7">
-        <v>0.2309243697478992</v>
+        <v>-0.0122646064703042</v>
       </c>
       <c r="H7">
-        <v>0.2309243697478992</v>
+        <v>-0.0122646064703042</v>
       </c>
       <c r="I7">
-        <v>0.02470588235294117</v>
+        <v>0.04297440849831</v>
       </c>
       <c r="J7">
-        <v>0.01538290788013319</v>
+        <v>0.04145377558221595</v>
       </c>
       <c r="K7">
-        <v>9.91</v>
+        <v>26.3</v>
       </c>
       <c r="L7">
-        <v>0.01665546218487395</v>
+        <v>0.04233059713503944</v>
       </c>
       <c r="M7">
-        <v>13.3</v>
+        <v>16</v>
       </c>
       <c r="N7">
-        <v>0.03409382209689823</v>
+        <v>0.02961865975564605</v>
       </c>
       <c r="O7">
-        <v>1.342078708375378</v>
+        <v>0.6083650190114068</v>
       </c>
       <c r="P7">
-        <v>13.3</v>
+        <v>16</v>
       </c>
       <c r="Q7">
-        <v>0.03409382209689823</v>
+        <v>0.02961865975564605</v>
       </c>
       <c r="R7">
-        <v>1.342078708375378</v>
+        <v>0.6083650190114068</v>
       </c>
       <c r="S7">
         <v>0</v>
@@ -1258,67 +1279,73 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>60</v>
+        <v>44.2</v>
       </c>
       <c r="V7">
-        <v>0.1538067162266085</v>
+        <v>0.08182154757497223</v>
       </c>
       <c r="W7">
-        <v>0.01758651286601597</v>
+        <v>0.05258948210357928</v>
       </c>
       <c r="X7">
-        <v>0.1096462801656766</v>
+        <v>0.09265845657407197</v>
       </c>
       <c r="Y7">
-        <v>-0.09205976729966064</v>
+        <v>-0.04006897447049269</v>
       </c>
       <c r="Z7">
-        <v>1.377633711507293</v>
+        <v>1.581720977596741</v>
       </c>
       <c r="AA7">
-        <v>0.02119201247668267</v>
+        <v>0.06556830643897853</v>
       </c>
       <c r="AB7">
-        <v>0.1019938164914625</v>
+        <v>0.09020410023256303</v>
       </c>
       <c r="AC7">
-        <v>-0.08080180401477978</v>
+        <v>-0.02463579379358451</v>
       </c>
       <c r="AD7">
-        <v>74.09999999999999</v>
+        <v>37.6</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>74.09999999999999</v>
+        <v>37.6</v>
       </c>
       <c r="AG7">
-        <v>14.09999999999999</v>
+        <v>-6.600000000000001</v>
       </c>
       <c r="AH7">
-        <v>0.1596294700560103</v>
+        <v>0.06507442021460713</v>
       </c>
       <c r="AI7">
-        <v>0.1290491118077325</v>
+        <v>0.06784554312522555</v>
       </c>
       <c r="AJ7">
-        <v>0.03488372093023254</v>
+        <v>-0.0123688155922039</v>
       </c>
       <c r="AK7">
-        <v>0.02742123687281212</v>
+        <v>-0.01294117647058824</v>
       </c>
       <c r="AL7">
-        <v>0</v>
+        <v>0.041</v>
       </c>
       <c r="AM7">
-        <v>0</v>
+        <v>0.041</v>
       </c>
       <c r="AN7">
-        <v>1.834158415841584</v>
+        <v>1</v>
+      </c>
+      <c r="AO7">
+        <v>651.2195121951219</v>
       </c>
       <c r="AP7">
-        <v>0.3490099009900989</v>
+        <v>-0.1755319148936171</v>
+      </c>
+      <c r="AQ7">
+        <v>651.2195121951219</v>
       </c>
     </row>
   </sheetData>
